--- a/clustering/8 subclusters (factoriescap_r (costs_r) 0 prop IQR).xlsx
+++ b/clustering/8 subclusters (factoriescap_r (costs_r) 0 prop IQR).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>clust</t>
   </si>
@@ -47,12 +47,15 @@
   <si>
     <t>trainingcosts_s</t>
   </si>
+  <si>
+    <t>Медианы кластеров</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +81,15 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -128,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -157,6 +169,7 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -463,6 +476,7 @@
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
@@ -760,6 +774,11 @@
       <c r="E20" s="9">
         <f t="shared" si="0"/>
         <v>8.6232368242988855E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
